--- a/assets/constructions/examples/ctd_inserts_threading_2surf.xlsx
+++ b/assets/constructions/examples/ctd_inserts_threading_2surf.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ctd" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="ctd" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BC6"/>
+  <dimension ref="A1:BH6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -704,11 +704,36 @@
           <t>releasepack</t>
         </is>
       </c>
+      <c r="BD1" s="1" t="inlineStr">
+        <is>
+          <t>lcs</t>
+        </is>
+      </c>
+      <c r="BE1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue</t>
+        </is>
+      </c>
+      <c r="BF1" s="1" t="inlineStr">
+        <is>
+          <t>pricecurrency</t>
+        </is>
+      </c>
+      <c r="BG1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue_rub</t>
+        </is>
+      </c>
+      <c r="BH1" s="1" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>6BEI11.5NPT-TM2VTX</t>
+          <t>3EI16WTM2VTX</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -723,7 +748,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VAR_3/4B</t>
+          <t>VAR_3/8V</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -749,7 +774,7 @@
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="n">
-        <v>35.34</v>
+        <v>14.29</v>
       </c>
       <c r="N2" t="n">
         <v>15</v>
@@ -757,17 +782,15 @@
       <c r="O2" t="n">
         <v>4</v>
       </c>
-      <c r="P2" t="n">
-        <v>16</v>
-      </c>
+      <c r="P2" t="inlineStr"/>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>6BEI11.5NPT-TM2...</t>
+          <t>3EI16WTM2...</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>6BEI11.5NPT-TM2...</t>
+          <t>3EI16WTM2...</t>
         </is>
       </c>
       <c r="S2" t="inlineStr"/>
@@ -787,10 +810,10 @@
         </is>
       </c>
       <c r="AC2" t="n">
-        <v>11.5</v>
+        <v>16</v>
       </c>
       <c r="AD2" t="n">
-        <v>11.5</v>
+        <v>16</v>
       </c>
       <c r="AE2" t="inlineStr"/>
       <c r="AF2" t="inlineStr"/>
@@ -798,13 +821,13 @@
       <c r="AH2" t="inlineStr"/>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>NPT60</t>
+          <t>WH55</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr"/>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>NPT</t>
+          <t>G</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr"/>
@@ -819,7 +842,7 @@
       <c r="AQ2" t="inlineStr"/>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>VARGUS_3/4TEI_B_TM</t>
+          <t>VARGUS_3/8T_TMC</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -863,11 +886,30 @@
           <t>2018/VARGUS2018-ENGweb.pdf</t>
         </is>
       </c>
+      <c r="BD2" t="n">
+        <v>1</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>45.2</v>
+      </c>
+      <c r="BF2" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="BG2" t="n">
+        <v>4155.4</v>
+      </c>
+      <c r="BH2" t="inlineStr">
+        <is>
+          <t>PMKNSH</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>3EI14WTM2VBX</t>
+          <t>5EI11BSPT-TM2VK2</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -882,7 +924,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VAR_3/8V</t>
+          <t>VAR_5/8V</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -892,7 +934,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>PMKNSH</t>
+          <t>NS</t>
         </is>
       </c>
       <c r="G3" t="inlineStr"/>
@@ -908,7 +950,7 @@
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="n">
-        <v>14.51</v>
+        <v>23.09</v>
       </c>
       <c r="N3" t="n">
         <v>15</v>
@@ -916,15 +958,17 @@
       <c r="O3" t="n">
         <v>4</v>
       </c>
-      <c r="P3" t="inlineStr"/>
+      <c r="P3" t="n">
+        <v>10</v>
+      </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>3EI14WTM2...</t>
+          <t>5EI11BSPT-TM2...</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>3EI14WTM2...</t>
+          <t>5EI11BSPT-TM2...</t>
         </is>
       </c>
       <c r="S3" t="inlineStr"/>
@@ -944,10 +988,10 @@
         </is>
       </c>
       <c r="AC3" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="AD3" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="AE3" t="inlineStr"/>
       <c r="AF3" t="inlineStr"/>
@@ -955,13 +999,13 @@
       <c r="AH3" t="inlineStr"/>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>WH55</t>
+          <t>NPT60</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr"/>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>NPT</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr"/>
@@ -976,7 +1020,7 @@
       <c r="AQ3" t="inlineStr"/>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>VARGUS_3/8T_TMC</t>
+          <t>VARGUS_5/8T_TMC</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -986,17 +1030,17 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>VBX</t>
+          <t>VK2</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
         <is>
-          <t>TiCN</t>
+          <t>NONE</t>
         </is>
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>PVD</t>
+          <t>NONE</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr"/>
@@ -1020,31 +1064,42 @@
           <t>2018/VARGUS2018-ENGweb.pdf</t>
         </is>
       </c>
+      <c r="BD3" t="n">
+        <v>1</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>70.93000000000001</v>
+      </c>
+      <c r="BF3" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="BG3" t="n">
+        <v>6520.86</v>
+      </c>
+      <c r="BH3" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>3EI14NPSTM2VBX</t>
+          <t>30 I/E 16 PG PH7920</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>VARGUS</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>VAR_3/8V</t>
-        </is>
-      </c>
+          <t>PALBIT</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>VARGUS</t>
+          <t>PALBIT</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -1054,7 +1109,7 @@
       </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I4" t="n">
         <v>2</v>
@@ -1065,31 +1120,25 @@
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="n">
-        <v>14.51</v>
+        <v>30</v>
       </c>
       <c r="N4" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="O4" t="n">
-        <v>4</v>
-      </c>
-      <c r="P4" t="n">
-        <v>8</v>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>3EI14NPSTM2...</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
         <is>
-          <t>3EI14NPSTM2...</t>
+          <t>30I/E16PG</t>
         </is>
       </c>
       <c r="S4" t="inlineStr"/>
       <c r="T4" t="inlineStr"/>
       <c r="U4" t="n">
-        <v>55</v>
+        <v>90</v>
       </c>
       <c r="V4" t="inlineStr"/>
       <c r="W4" t="inlineStr"/>
@@ -1103,10 +1152,10 @@
         </is>
       </c>
       <c r="AC4" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AD4" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AE4" t="inlineStr"/>
       <c r="AF4" t="inlineStr"/>
@@ -1114,13 +1163,13 @@
       <c r="AH4" t="inlineStr"/>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>NPT60</t>
+          <t>PG80</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr"/>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>NPT</t>
+          <t>Pg 21</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr"/>
@@ -1135,7 +1184,7 @@
       <c r="AQ4" t="inlineStr"/>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>VARGUS_3/8T_TMNC16</t>
+          <t>PALB_A30</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1145,12 +1194,12 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>VBX</t>
+          <t>PH7920</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>TiCN</t>
+          <t>AlTiN</t>
         </is>
       </c>
       <c r="AV4" t="inlineStr">
@@ -1176,14 +1225,33 @@
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>2018/VARGUS2018-ENGweb.pdf</t>
+          <t>2022/ основной каталог Palbit</t>
+        </is>
+      </c>
+      <c r="BD4" t="n">
+        <v>1</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>173.57</v>
+      </c>
+      <c r="BF4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="BG4" t="n">
+        <v>15956.93</v>
+      </c>
+      <c r="BH4" t="inlineStr">
+        <is>
+          <t>PMKNSH</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>3E18NPT-TM2VTX</t>
+          <t>5EI16WTM2VBX</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1198,7 +1266,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VAR_3/8V</t>
+          <t>VAR_5/8V</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1224,7 +1292,7 @@
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="n">
-        <v>14.11</v>
+        <v>25.4</v>
       </c>
       <c r="N5" t="n">
         <v>15</v>
@@ -1232,17 +1300,15 @@
       <c r="O5" t="n">
         <v>4</v>
       </c>
-      <c r="P5" t="n">
-        <v>10</v>
-      </c>
+      <c r="P5" t="inlineStr"/>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>3E18NPT-TM2... *</t>
+          <t>5EI16WTM2...</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>3E18NPT-TM2... *</t>
+          <t>5EI16WTM2...</t>
         </is>
       </c>
       <c r="S5" t="inlineStr"/>
@@ -1262,10 +1328,10 @@
         </is>
       </c>
       <c r="AC5" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AD5" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AE5" t="inlineStr"/>
       <c r="AF5" t="inlineStr"/>
@@ -1273,13 +1339,13 @@
       <c r="AH5" t="inlineStr"/>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>NPT60</t>
+          <t>WH55</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr"/>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>NPT</t>
+          <t>G</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr"/>
@@ -1294,7 +1360,7 @@
       <c r="AQ5" t="inlineStr"/>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>VARGUS_3/8T_TMNC</t>
+          <t>VARGUS_5/8T_TMC</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -1304,12 +1370,12 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>VTX</t>
+          <t>VBX</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>TiAlN</t>
+          <t>TiCN</t>
         </is>
       </c>
       <c r="AV5" t="inlineStr">
@@ -1338,11 +1404,30 @@
           <t>2018/VARGUS2018-ENGweb.pdf</t>
         </is>
       </c>
+      <c r="BD5" t="n">
+        <v>1</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>86.45999999999999</v>
+      </c>
+      <c r="BF5" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="BG5" t="n">
+        <v>7948.59</v>
+      </c>
+      <c r="BH5" t="inlineStr">
+        <is>
+          <t>PMKNSH</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>5EI11.5NPT-TM2VBX</t>
+          <t>3EI16WTM2VBX</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1357,7 +1442,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VAR_5/8V</t>
+          <t>VAR_3/8V</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1383,7 +1468,7 @@
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="n">
-        <v>24.3</v>
+        <v>14.29</v>
       </c>
       <c r="N6" t="n">
         <v>15</v>
@@ -1391,17 +1476,15 @@
       <c r="O6" t="n">
         <v>4</v>
       </c>
-      <c r="P6" t="n">
-        <v>11</v>
-      </c>
+      <c r="P6" t="inlineStr"/>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>5EI11.5NPT-TM2...</t>
+          <t>3EI16WTM2...</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>5EI11.5NPT-TM2...</t>
+          <t>3EI16WTM2...</t>
         </is>
       </c>
       <c r="S6" t="inlineStr"/>
@@ -1421,10 +1504,10 @@
         </is>
       </c>
       <c r="AC6" t="n">
-        <v>11.5</v>
+        <v>16</v>
       </c>
       <c r="AD6" t="n">
-        <v>11.5</v>
+        <v>16</v>
       </c>
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr"/>
@@ -1432,13 +1515,13 @@
       <c r="AH6" t="inlineStr"/>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>NPT60</t>
+          <t>WH55</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr"/>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>NPT</t>
+          <t>G</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr"/>
@@ -1453,7 +1536,7 @@
       <c r="AQ6" t="inlineStr"/>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>VARGUS_5/8T_TMC</t>
+          <t>VARGUS_3/8T_TMC</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -1495,6 +1578,25 @@
       <c r="BC6" t="inlineStr">
         <is>
           <t>2018/VARGUS2018-ENGweb.pdf</t>
+        </is>
+      </c>
+      <c r="BD6" t="n">
+        <v>1</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>45.2</v>
+      </c>
+      <c r="BF6" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="BG6" t="n">
+        <v>4155.4</v>
+      </c>
+      <c r="BH6" t="inlineStr">
+        <is>
+          <t>PMKNSH</t>
         </is>
       </c>
     </row>
